--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3594,8 +3710,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3610,1027 +3730,1215 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">낭낭 십팔세 — 민요채보-2/낭낭 십팔세.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">낭낭 십팔세</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="L3" s="13"/>
+      <c r="M3" s="15"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="L4" s="13"/>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="L5" s="13"/>
+      <c r="M5" s="16"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="L6" s="13"/>
+      <c r="M6" s="18"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-―
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-―
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-―
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-―
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="L7" s="13"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀</t>
         </is>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="L8" s="13"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">얜</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="L9" s="13"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I10" s="18"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 姑
 仲</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">꿍</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="L11" s="13"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰
-―
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="L12" s="13"/>
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="L13" s="13"/>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="18"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">때</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 仲</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 仲</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="L14" s="13"/>
+      <c r="M14" s="18"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">읍</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">낭</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">낭</t>
         </is>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="L15" s="13"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="L16" s="13"/>
+      <c r="M16" s="16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="L17" s="13"/>
+      <c r="M17" s="16"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">웁</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="18"/>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3099,7 +3099,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
@@ -3112,7 +3112,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3167,7 +3167,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3440,13 +3440,13 @@
       <c r="A18" s="0"/>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E18" s="10"/>
@@ -3458,7 +3458,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="10"/>

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2912,560 +2953,560 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">낭낭 십팔세</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="8"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="9"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="9"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 南</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 南</t>
         </is>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="28"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="28"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="10"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="24"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G7" s="24"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="8"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="9"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="25"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="9"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="28"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="10"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="8"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 太</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 㳞</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="9"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="26"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 無</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 太</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 無</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 無</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="24"/>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="G15" s="24"/>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="8"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="9"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="9"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="27"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="27"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="10"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -2934,24 +2934,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
       <c r="L4" s="23"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       <c r="L5" s="23"/>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
       <c r="L6" s="23"/>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       <c r="C8" s="25"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3170,7 +3170,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       <c r="L10" s="23"/>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       <c r="L12" s="23"/>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       <c r="L13" s="23"/>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
       <c r="L14" s="23"/>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       <c r="L16" s="23"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
       <c r="L17" s="23"/>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -346,7 +346,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -355,7 +354,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -407,7 +405,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -416,7 +413,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -457,7 +453,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -466,7 +461,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -488,7 +482,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -497,7 +490,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -511,7 +503,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -520,7 +511,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -546,7 +536,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -555,7 +544,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -580,7 +568,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -589,7 +576,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -660,7 +646,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -670,7 +655,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -685,7 +669,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -694,17 +678,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -737,6 +721,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -829,7 +819,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -895,6 +885,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3257,420 +3299,420 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="12.67"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="23" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="23" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="27" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="21" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="23"/>
+      <c r="F8" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="23" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="11" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="11" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="11" t="s">
+      <c r="G10" s="28"/>
+      <c r="H10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="21" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="23" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="23" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="27" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="21" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="23" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="23"/>
+      <c r="F17" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="23" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="11" t="s">
+      <c r="C18" s="27"/>
+      <c r="D18" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="11" t="s">
+      <c r="E18" s="27"/>
+      <c r="F18" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="11" t="s">
+      <c r="G18" s="27"/>
+      <c r="H18" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="I18" s="14"/>
+      <c r="I18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -743,10 +743,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -344,22 +344,8 @@
     <t xml:space="preserve">저</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">–
+南無</t>
   </si>
   <si>
     <t xml:space="preserve">쩍</t>
@@ -403,22 +389,8 @@
     <t xml:space="preserve">름</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">汰
+–㴌</t>
   </si>
   <si>
     <t xml:space="preserve">울
@@ -451,22 +423,8 @@
     <t xml:space="preserve">서</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">南
+㳞</t>
   </si>
   <si>
     <t xml:space="preserve">떠
@@ -480,49 +438,21 @@
     <t xml:space="preserve">누</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">간</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">–
 汰</t>
   </si>
   <si>
+    <t xml:space="preserve">간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+湳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+汰</t>
+  </si>
+  <si>
     <t xml:space="preserve">새</t>
   </si>
   <si>
@@ -534,22 +464,8 @@
 를</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">㴌
+–汰</t>
   </si>
   <si>
     <t xml:space="preserve">그
@@ -566,22 +482,8 @@
 다</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">南
+無</t>
   </si>
   <si>
     <t xml:space="preserve">운
@@ -644,22 +546,8 @@
     <t xml:space="preserve">세</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+    <t xml:space="preserve">–
+△</t>
   </si>
 </sst>
 </file>
@@ -3290,7 +3178,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:I18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3307,7 +3195,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="12.67"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="57.14" customHeight="true">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -3319,7 +3208,7 @@
       <c r="H2" s="19"/>
       <c r="I2" s="19"/>
     </row>
-    <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B3" s="20" t="s">
         <v>47</v>
       </c>
@@ -3345,7 +3234,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B4" s="22" t="s">
         <v>100</v>
       </c>
@@ -3371,7 +3260,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B5" s="24" t="s">
         <v>51</v>
       </c>
@@ -3397,7 +3286,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B6" s="24" t="s">
         <v>52</v>
       </c>
@@ -3423,7 +3312,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B7" s="26" t="s">
         <v>113</v>
       </c>
@@ -3449,7 +3338,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B8" s="20" t="s">
         <v>57</v>
       </c>
@@ -3473,7 +3362,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B9" s="24" t="s">
         <v>49</v>
       </c>
@@ -3497,7 +3386,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B10" s="24" t="s">
         <v>59</v>
       </c>
@@ -3515,7 +3404,7 @@
       </c>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B11" s="26" t="s">
         <v>122</v>
       </c>
@@ -3541,7 +3430,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B12" s="22" t="s">
         <v>126</v>
       </c>
@@ -3567,7 +3456,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B13" s="22" t="s">
         <v>133</v>
       </c>
@@ -3593,7 +3482,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B14" s="22" t="s">
         <v>138</v>
       </c>
@@ -3619,7 +3508,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B15" s="24" t="s">
         <v>66</v>
       </c>
@@ -3645,7 +3534,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B16" s="24" t="s">
         <v>66</v>
       </c>
@@ -3669,7 +3558,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B17" s="24" t="s">
         <v>68</v>
       </c>
@@ -3693,7 +3582,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B18" s="24" t="s">
         <v>155</v>
       </c>
@@ -3717,7 +3606,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/낭낭 십팔세.xlsx
+++ b/sheets/민요/검수/낭낭 십팔세.xlsx
@@ -3184,15 +3184,18 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16381" min="16381" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
